--- a/data/trans_orig/P05A05-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P05A05-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2007 (tasa de respuesta: 99,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58872</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88290</t>
+          <t>86988</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39249</t>
+          <t>40357</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66164</t>
+          <t>66352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106892</t>
+          <t>105709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148019</t>
+          <t>147562</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>161507</t>
+          <t>160156</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>192707</t>
+          <t>192145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>173825</t>
+          <t>174158</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203209</t>
+          <t>203280</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>343135</t>
+          <t>344708</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>387069</t>
+          <t>390160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,86%</t>
+          <t>73,44%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31428</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10692</t>
+          <t>11361</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28035</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28753</t>
+          <t>28252</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>52899</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>121087</t>
+          <t>119168</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>160703</t>
+          <t>160235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>130833</t>
+          <t>133097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173198</t>
+          <t>173863</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>262765</t>
+          <t>264762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>319879</t>
+          <t>320885</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,12%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>211711</t>
+          <t>212790</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>258037</t>
+          <t>259162</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>214417</t>
+          <t>213749</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>258377</t>
+          <t>258461</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>441019</t>
+          <t>438994</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>505440</t>
+          <t>506435</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99349</t>
+          <t>97803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>137518</t>
+          <t>135869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96251</t>
+          <t>97087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>133386</t>
+          <t>132823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>206945</t>
+          <t>206758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>259536</t>
+          <t>260315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,14%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>108961</t>
+          <t>110173</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144968</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34,17%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>89713</t>
+          <t>89526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122904</t>
+          <t>124843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>210153</t>
+          <t>208475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>260239</t>
+          <t>257580</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,43%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139454</t>
+          <t>137637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>175832</t>
+          <t>173368</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>157557</t>
+          <t>158479</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>194564</t>
+          <t>194828</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>306363</t>
+          <t>308568</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>357954</t>
+          <t>360811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>24540</t>
+          <t>24023</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48870</t>
+          <t>48880</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>39987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>65439</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>69287</t>
+          <t>70630</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>106227</t>
+          <t>105448</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>88692</t>
+          <t>87709</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122296</t>
+          <t>121232</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99988</t>
+          <t>98109</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>132671</t>
+          <t>133888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>197962</t>
+          <t>198210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>245454</t>
+          <t>243961</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,5%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183606</t>
+          <t>184207</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>221141</t>
+          <t>220405</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,33%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>193487</t>
+          <t>190107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>229043</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>386297</t>
+          <t>387033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>439887</t>
+          <t>439305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,4%</t>
+          <t>60,32%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37885</t>
+          <t>37936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66057</t>
+          <t>65272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>33223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>58140</t>
+          <t>57294</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>77761</t>
+          <t>77881</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>115984</t>
+          <t>114475</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13684</t>
+          <t>12919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31334</t>
+          <t>31211</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27801</t>
+          <t>26388</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53262</t>
+          <t>50590</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93644</t>
+          <t>93482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123950</t>
+          <t>122602</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,23%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94123</t>
+          <t>92534</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>122672</t>
+          <t>120843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>194591</t>
+          <t>196486</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>233801</t>
+          <t>235896</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>57,38%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>62402</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>90489</t>
+          <t>91488</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61968</t>
+          <t>63089</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>91390</t>
+          <t>92525</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>134054</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>172764</t>
+          <t>172514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,34%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>91338</t>
+          <t>91244</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>121870</t>
+          <t>123070</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84889</t>
+          <t>84429</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>116562</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>182925</t>
+          <t>186606</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>231123</t>
+          <t>229817</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,01%</t>
         </is>
       </c>
     </row>
@@ -3126,12 +3126,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130138</t>
+          <t>130425</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>162242</t>
+          <t>161875</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>135312</t>
+          <t>134148</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>168727</t>
+          <t>167632</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3176,12 +3176,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>60,66%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>273912</t>
+          <t>274295</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>321305</t>
+          <t>320076</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,52%</t>
         </is>
       </c>
     </row>
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8980</t>
+          <t>9675</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25634</t>
+          <t>24887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17447</t>
+          <t>18040</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>36436</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3289,12 +3289,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30734</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>54929</t>
+          <t>54735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>275921</t>
+          <t>277444</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>323166</t>
+          <t>325717</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,11%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>243741</t>
+          <t>244105</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>294545</t>
+          <t>294882</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>46,15%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>531845</t>
+          <t>532529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>605597</t>
+          <t>605857</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>48,34%</t>
         </is>
       </c>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>247221</t>
+          <t>246917</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>296468</t>
+          <t>296025</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3597,12 +3597,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>283810</t>
+          <t>286582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>334455</t>
+          <t>335602</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3632,12 +3632,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>542105</t>
+          <t>544334</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>616028</t>
+          <t>617773</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -3695,12 +3695,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>31412</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59961</t>
+          <t>57723</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3710,12 +3710,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>45184</t>
+          <t>45496</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>75025</t>
+          <t>75714</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>85276</t>
+          <t>85531</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>124297</t>
+          <t>125962</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>179750</t>
+          <t>180737</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>230394</t>
+          <t>230225</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>206880</t>
+          <t>206387</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>256570</t>
+          <t>259624</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>399820</t>
+          <t>400550</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>469855</t>
+          <t>470202</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4010,12 +4010,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,96%</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>275613</t>
+          <t>275099</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>328397</t>
+          <t>327523</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,12 +4053,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>265032</t>
+          <t>265701</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>318685</t>
+          <t>320751</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>557256</t>
+          <t>551398</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>637324</t>
+          <t>633248</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -4151,12 +4151,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>209480</t>
+          <t>209429</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>262274</t>
+          <t>259511</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4166,12 +4166,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4186,12 +4186,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>230558</t>
+          <t>230267</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>281774</t>
+          <t>285136</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,54%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>453933</t>
+          <t>454205</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>527574</t>
+          <t>529003</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,83%</t>
         </is>
       </c>
     </row>
@@ -4381,12 +4381,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1022118</t>
+          <t>1020819</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1128639</t>
+          <t>1132825</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4396,12 +4396,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>995094</t>
+          <t>993982</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1106850</t>
+          <t>1104160</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2045308</t>
+          <t>2048112</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2201402</t>
+          <t>2193004</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,18%</t>
+          <t>33,05%</t>
         </is>
       </c>
     </row>
@@ -4494,12 +4494,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1537180</t>
+          <t>1540307</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1660123</t>
+          <t>1657325</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1618564</t>
+          <t>1614570</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1729902</t>
+          <t>1729953</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4544,7 +4544,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3192424</t>
+          <t>3184798</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3363682</t>
+          <t>3357488</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,6%</t>
         </is>
       </c>
     </row>
@@ -4607,12 +4607,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>550722</t>
+          <t>549875</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>639030</t>
+          <t>641177</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>598882</t>
+          <t>603895</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>694705</t>
+          <t>690548</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1178313</t>
+          <t>1174107</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1300924</t>
+          <t>1310400</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4692,12 +4692,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4878,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2012 (tasa de respuesta: 99,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5073,12 +5073,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108745</t>
+          <t>109226</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143965</t>
+          <t>144805</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5088,12 +5088,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5108,12 +5108,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105866</t>
+          <t>108356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>142752</t>
+          <t>143071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5143,12 +5143,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226961</t>
+          <t>226339</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276852</t>
+          <t>277541</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,8%</t>
         </is>
       </c>
     </row>
@@ -5186,12 +5186,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106877</t>
+          <t>107437</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142382</t>
+          <t>142314</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5201,12 +5201,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5221,12 +5221,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>115156</t>
+          <t>115064</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150867</t>
+          <t>150091</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5256,12 +5256,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234386</t>
+          <t>230770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>284233</t>
+          <t>283291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5271,12 +5271,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>49,81%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>26285</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>12331</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31703</t>
+          <t>32505</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44837</t>
+          <t>45011</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77832</t>
+          <t>76397</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -5529,12 +5529,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>118796</t>
+          <t>119245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>161212</t>
+          <t>161859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>132328</t>
+          <t>133113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174119</t>
+          <t>175865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>266068</t>
+          <t>264879</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325981</t>
+          <t>324653</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5614,12 +5614,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,74%</t>
         </is>
       </c>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>225684</t>
+          <t>224719</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>271353</t>
+          <t>270454</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5657,12 +5657,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,96%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5677,12 +5677,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>221833</t>
+          <t>221556</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>269347</t>
+          <t>269419</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5692,12 +5692,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5712,12 +5712,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>459719</t>
+          <t>459474</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>526199</t>
+          <t>527551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5727,12 +5727,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>51,44%</t>
+          <t>51,57%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93567</t>
+          <t>96003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134687</t>
+          <t>136102</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102327</t>
+          <t>101727</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143747</t>
+          <t>143005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208870</t>
+          <t>208501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>265969</t>
+          <t>266676</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -5985,12 +5985,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27684</t>
+          <t>27701</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>50102</t>
+          <t>52289</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6020,12 +6020,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>30571</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>53544</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6055,12 +6055,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>63830</t>
+          <t>62580</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96682</t>
+          <t>96026</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6070,12 +6070,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -6098,12 +6098,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155221</t>
+          <t>153255</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189781</t>
+          <t>189367</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6133,12 +6133,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148820</t>
+          <t>147887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185697</t>
+          <t>184950</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>312546</t>
+          <t>315607</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>363840</t>
+          <t>365780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>55,25%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>96335</t>
+          <t>93994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128616</t>
+          <t>129369</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114860</t>
+          <t>114370</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150363</t>
+          <t>149099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>217785</t>
+          <t>218665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>268224</t>
+          <t>266082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -6441,12 +6441,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>140965</t>
+          <t>140144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181367</t>
+          <t>179714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>143429</t>
+          <t>145552</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183696</t>
+          <t>184526</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>299608</t>
+          <t>294389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>356219</t>
+          <t>351126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>46,54%</t>
         </is>
       </c>
     </row>
@@ -6554,12 +6554,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>129961</t>
+          <t>130631</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>170095</t>
+          <t>170128</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6569,7 +6569,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>120993</t>
+          <t>120526</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>159422</t>
+          <t>158354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259780</t>
+          <t>261503</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>314290</t>
+          <t>315317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,79%</t>
         </is>
       </c>
     </row>
@@ -6667,12 +6667,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>45319</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74419</t>
+          <t>75314</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>66772</t>
+          <t>65877</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>99518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>120830</t>
+          <t>119879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>165030</t>
+          <t>162997</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6752,12 +6752,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -6897,12 +6897,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>17173</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35194</t>
+          <t>36367</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21151</t>
+          <t>21449</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42656</t>
+          <t>41664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>42357</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>71877</t>
+          <t>71771</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -7010,12 +7010,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>53391</t>
+          <t>52959</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>80102</t>
+          <t>80917</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67672</t>
+          <t>66101</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96891</t>
+          <t>95661</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,12%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126075</t>
+          <t>127286</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>165537</t>
+          <t>169468</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7095,12 +7095,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -7123,12 +7123,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>106772</t>
+          <t>106094</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135328</t>
+          <t>135499</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7158,12 +7158,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93519</t>
+          <t>93181</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122813</t>
+          <t>125143</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7193,12 +7193,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209013</t>
+          <t>207793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>251266</t>
+          <t>249251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7208,12 +7208,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>57,67%</t>
         </is>
       </c>
     </row>
@@ -7353,12 +7353,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23296</t>
+          <t>23047</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>44761</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>21399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43400</t>
+          <t>44698</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49170</t>
+          <t>51133</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>81236</t>
+          <t>84443</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7438,12 +7438,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -7466,12 +7466,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>108824</t>
+          <t>110826</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>142872</t>
+          <t>143090</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>129060</t>
+          <t>131106</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>163561</t>
+          <t>165261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,41%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>249490</t>
+          <t>250520</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>296694</t>
+          <t>297474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7551,12 +7551,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -7579,12 +7579,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97105</t>
+          <t>98457</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>131429</t>
+          <t>131124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>86092</t>
+          <t>85964</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>118269</t>
+          <t>117640</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>194319</t>
+          <t>191748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>241997</t>
+          <t>241794</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -7809,12 +7809,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>91175</t>
+          <t>89484</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>130837</t>
+          <t>130802</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -7844,12 +7844,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106434</t>
+          <t>107282</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>150523</t>
+          <t>150945</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7879,12 +7879,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>208888</t>
+          <t>205037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266001</t>
+          <t>263881</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7894,12 +7894,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -7922,12 +7922,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>340979</t>
+          <t>340434</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>396113</t>
+          <t>394911</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7937,12 +7937,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,45%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>59,86%</t>
+          <t>59,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7957,12 +7957,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>369266</t>
+          <t>370699</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>426468</t>
+          <t>425629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,5%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7992,12 +7992,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>729736</t>
+          <t>728941</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>803553</t>
+          <t>803472</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>160507</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>208160</t>
+          <t>209459</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8070,12 +8070,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>145285</t>
+          <t>143443</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>191853</t>
+          <t>191707</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8105,12 +8105,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>319511</t>
+          <t>317642</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>384415</t>
+          <t>386746</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8120,12 +8120,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,55%</t>
         </is>
       </c>
     </row>
@@ -8265,12 +8265,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>437294</t>
+          <t>440147</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>495032</t>
+          <t>495435</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8280,12 +8280,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8300,12 +8300,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>461184</t>
+          <t>464516</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>521401</t>
+          <t>524034</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>56,27%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8335,12 +8335,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>921214</t>
+          <t>926290</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1001745</t>
+          <t>1004339</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8350,12 +8350,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,83%</t>
         </is>
       </c>
     </row>
@@ -8378,12 +8378,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>172665</t>
+          <t>174279</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>225399</t>
+          <t>225000</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8393,12 +8393,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8413,12 +8413,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>183999</t>
+          <t>180194</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>237949</t>
+          <t>234683</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8428,12 +8428,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8448,12 +8448,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>366966</t>
+          <t>369343</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>439554</t>
+          <t>440788</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8463,12 +8463,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -8491,12 +8491,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>94715</t>
+          <t>95764</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>134309</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8506,12 +8506,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>98720</t>
+          <t>98440</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>142268</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8541,12 +8541,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>203385</t>
+          <t>204070</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>259932</t>
+          <t>262717</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8576,12 +8576,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -8721,12 +8721,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1044329</t>
+          <t>1045744</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1160263</t>
+          <t>1161026</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8756,12 +8756,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1111024</t>
+          <t>1115924</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1230356</t>
+          <t>1226746</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8791,12 +8791,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2181424</t>
+          <t>2186277</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2353032</t>
+          <t>2346598</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8806,12 +8806,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>33,78%</t>
         </is>
       </c>
     </row>
@@ -8834,12 +8834,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1388495</t>
+          <t>1385916</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1510917</t>
+          <t>1512008</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8849,12 +8849,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,65%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8869,12 +8869,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1454052</t>
+          <t>1458119</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1578408</t>
+          <t>1569442</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8884,12 +8884,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8904,12 +8904,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2883046</t>
+          <t>2889649</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3060613</t>
+          <t>3064122</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8919,12 +8919,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -8947,12 +8947,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>808419</t>
+          <t>798675</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>915311</t>
+          <t>907549</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8962,12 +8962,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8982,12 +8982,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>806088</t>
+          <t>806960</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>907061</t>
+          <t>913131</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9017,12 +9017,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1643546</t>
+          <t>1637211</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1793226</t>
+          <t>1782199</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9032,12 +9032,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2016 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9413,12 +9413,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108310</t>
+          <t>108888</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143870</t>
+          <t>145152</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9428,12 +9428,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>114566</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147630</t>
+          <t>149032</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>232616</t>
+          <t>234125</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>282212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100822</t>
+          <t>98727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134754</t>
+          <t>135984</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90633</t>
+          <t>90362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>126733</t>
+          <t>123760</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9596,12 +9596,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>199785</t>
+          <t>198530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247106</t>
+          <t>245334</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32695</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57634</t>
+          <t>58229</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37096</t>
+          <t>36865</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>63032</t>
+          <t>64190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77463</t>
+          <t>75322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>113918</t>
+          <t>110862</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9724,12 +9724,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -9869,12 +9869,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83276</t>
+          <t>81898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>118674</t>
+          <t>118398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9884,12 +9884,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9904,12 +9904,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92961</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>131950</t>
+          <t>131109</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9939,12 +9939,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>186369</t>
+          <t>184438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>242399</t>
+          <t>236692</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9954,12 +9954,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,15%</t>
         </is>
       </c>
     </row>
@@ -9982,12 +9982,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>199488</t>
+          <t>200219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>243456</t>
+          <t>247356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9997,12 +9997,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>49,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223363</t>
+          <t>221165</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>268875</t>
+          <t>267019</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10032,12 +10032,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>42,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10052,12 +10052,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>434321</t>
+          <t>437062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>501939</t>
+          <t>504032</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10067,12 +10067,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,29%</t>
         </is>
       </c>
     </row>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160691</t>
+          <t>159288</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>204006</t>
+          <t>201644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10110,12 +10110,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>141122</t>
+          <t>142909</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>183759</t>
+          <t>186377</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10145,12 +10145,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10165,12 +10165,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311411</t>
+          <t>314964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>373945</t>
+          <t>379096</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10180,12 +10180,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -10325,12 +10325,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45955</t>
+          <t>45313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>71232</t>
+          <t>70285</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10340,12 +10340,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10360,12 +10360,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58947</t>
+          <t>59729</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>88012</t>
+          <t>88025</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113642</t>
+          <t>109346</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>151481</t>
+          <t>149464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10410,12 +10410,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -10438,12 +10438,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157578</t>
+          <t>158035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191682</t>
+          <t>190957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10453,12 +10453,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10473,12 +10473,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158857</t>
+          <t>157114</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192400</t>
+          <t>192302</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10488,12 +10488,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>324337</t>
+          <t>322476</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>371658</t>
+          <t>373085</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10523,12 +10523,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,83%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -10551,12 +10551,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71058</t>
+          <t>70557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103213</t>
+          <t>101529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10566,12 +10566,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72674</t>
+          <t>72525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>105762</t>
+          <t>105358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10601,12 +10601,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10621,12 +10621,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153902</t>
+          <t>151448</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>195734</t>
+          <t>196101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -10781,12 +10781,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150260</t>
+          <t>149910</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>189771</t>
+          <t>189694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,13%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10816,12 +10816,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>174513</t>
+          <t>176224</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>214846</t>
+          <t>216119</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337564</t>
+          <t>337136</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>394733</t>
+          <t>395685</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10866,12 +10866,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,81%</t>
         </is>
       </c>
     </row>
@@ -10894,12 +10894,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123437</t>
+          <t>124390</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>162185</t>
+          <t>162910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10929,12 +10929,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>109760</t>
+          <t>109219</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>147522</t>
+          <t>146722</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10944,12 +10944,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10964,12 +10964,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247065</t>
+          <t>243975</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>299966</t>
+          <t>299053</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,91%</t>
         </is>
       </c>
     </row>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>40124</t>
+          <t>39696</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>65755</t>
+          <t>66975</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11022,12 +11022,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11042,12 +11042,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45236</t>
+          <t>45146</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73428</t>
+          <t>73992</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92351</t>
+          <t>92720</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>131513</t>
+          <t>132105</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -11237,12 +11237,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115894</t>
+          <t>115453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142701</t>
+          <t>143380</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11252,12 +11252,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11272,12 +11272,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>127390</t>
+          <t>126613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>155519</t>
+          <t>155748</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11287,12 +11287,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11307,12 +11307,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251561</t>
+          <t>252547</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>291496</t>
+          <t>289694</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11322,12 +11322,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,4%</t>
         </is>
       </c>
     </row>
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>44090</t>
+          <t>43501</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>70261</t>
+          <t>69983</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11365,49 +11365,49 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
+          <t>33,13%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>56338</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>45213</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>72702</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
           <t>33,26%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>56338</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>44325</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>70623</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>20,28%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>32,31%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -11420,12 +11420,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>94708</t>
+          <t>95959</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130818</t>
+          <t>130293</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -11463,12 +11463,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>37580</t>
+          <t>36113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11478,12 +11478,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11498,12 +11498,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12040</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29552</t>
+          <t>28194</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>35235</t>
+          <t>35056</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60696</t>
+          <t>59298</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,8%</t>
         </is>
       </c>
     </row>
@@ -11693,12 +11693,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>44804</t>
+          <t>43412</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>72020</t>
+          <t>71876</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11708,12 +11708,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11728,12 +11728,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60803</t>
+          <t>60843</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>90060</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>111521</t>
+          <t>108659</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>151550</t>
+          <t>149773</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -11806,12 +11806,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>104720</t>
+          <t>104886</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>137022</t>
+          <t>138111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11821,12 +11821,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11841,12 +11841,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>114720</t>
+          <t>115771</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148787</t>
+          <t>150151</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>229998</t>
+          <t>230633</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>277065</t>
+          <t>275490</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -11919,12 +11919,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71627</t>
+          <t>70519</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>101071</t>
+          <t>101214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11934,12 +11934,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11954,12 +11954,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>51872</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80969</t>
+          <t>79886</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11969,12 +11969,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11989,12 +11989,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>130696</t>
+          <t>131582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>173527</t>
+          <t>173107</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12004,12 +12004,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,42%</t>
+          <t>32,34%</t>
         </is>
       </c>
     </row>
@@ -12149,12 +12149,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>173716</t>
+          <t>177736</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>223533</t>
+          <t>231536</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12164,12 +12164,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -12184,12 +12184,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>189130</t>
+          <t>188155</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>237932</t>
+          <t>239729</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>375992</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>449824</t>
+          <t>447664</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -12262,12 +12262,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>281162</t>
+          <t>279557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>337189</t>
+          <t>335680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,36%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12297,12 +12297,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>297543</t>
+          <t>295201</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>350898</t>
+          <t>351934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12312,12 +12312,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>51,07%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12332,12 +12332,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>592693</t>
+          <t>593056</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>668797</t>
+          <t>668422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,75%</t>
         </is>
       </c>
     </row>
@@ -12375,12 +12375,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>127895</t>
+          <t>127187</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>172013</t>
+          <t>172392</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -12390,12 +12390,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -12410,12 +12410,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>130393</t>
+          <t>129854</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>176866</t>
+          <t>176613</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -12425,12 +12425,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -12445,12 +12445,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>267875</t>
+          <t>269068</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>334587</t>
+          <t>334315</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -12605,12 +12605,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>398970</t>
+          <t>399981</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>456540</t>
+          <t>453813</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -12620,12 +12620,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>434155</t>
+          <t>434330</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>496089</t>
+          <t>493275</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12655,12 +12655,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12675,12 +12675,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>854834</t>
+          <t>853344</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>935565</t>
+          <t>935029</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12690,12 +12690,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,35%</t>
         </is>
       </c>
     </row>
@@ -12718,12 +12718,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>170069</t>
+          <t>171713</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>216608</t>
+          <t>218611</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12753,12 +12753,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>162561</t>
+          <t>164468</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>209860</t>
+          <t>213083</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12768,12 +12768,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12788,12 +12788,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>344748</t>
+          <t>347504</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>414514</t>
+          <t>416399</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -12831,12 +12831,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>132692</t>
+          <t>132813</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>178665</t>
+          <t>179871</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12846,12 +12846,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12866,12 +12866,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>147038</t>
+          <t>149209</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>196924</t>
+          <t>198143</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12881,12 +12881,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12901,12 +12901,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>294733</t>
+          <t>296498</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>361017</t>
+          <t>363173</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -13061,12 +13061,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1200614</t>
+          <t>1205618</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1320159</t>
+          <t>1320986</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13096,12 +13096,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1345036</t>
+          <t>1349350</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1467578</t>
+          <t>1466807</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13111,12 +13111,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13131,12 +13131,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>2594422</t>
+          <t>2584107</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>2757183</t>
+          <t>2752705</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13146,12 +13146,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1275693</t>
+          <t>1284468</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1396378</t>
+          <t>1397976</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,34%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13209,12 +13209,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1296826</t>
+          <t>1293371</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1415686</t>
+          <t>1409948</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13224,12 +13224,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13244,12 +13244,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2595275</t>
+          <t>2605102</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2766095</t>
+          <t>2770010</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13259,12 +13259,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -13287,12 +13287,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>732286</t>
+          <t>730207</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>831179</t>
+          <t>830573</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13322,12 +13322,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>719000</t>
+          <t>719031</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>818859</t>
+          <t>817253</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13342,7 +13342,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13357,12 +13357,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1480348</t>
+          <t>1473339</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1618375</t>
+          <t>1621826</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13372,12 +13372,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,47%</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023</t>
+          <t>Población según si en el barrio donde vive hay espacios verdes suficientes en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13753,12 +13753,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18636</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -13768,12 +13768,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13788,12 +13788,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4998</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13803,47 +13803,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,11%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>16618</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>10422</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>29150</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>16618</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>10215</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>27823</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29939</t>
+          <t>27750</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13881,12 +13881,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>6093</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13916,12 +13916,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39315</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -13979,12 +13979,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>271954</t>
+          <t>272182</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>293761</t>
+          <t>293756</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -13994,7 +13994,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -14014,12 +14014,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>264869</t>
+          <t>263254</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>276917</t>
+          <t>276616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -14029,12 +14029,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -14049,12 +14049,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>541080</t>
+          <t>541889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>567530</t>
+          <t>567459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -14209,12 +14209,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17144</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42788</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -14224,12 +14224,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -14244,12 +14244,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -14259,12 +14259,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14279,12 +14279,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>46636</t>
+          <t>46860</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>79081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14294,12 +14294,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -14322,12 +14322,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>96268</t>
+          <t>93937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>145537</t>
+          <t>144020</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -14337,12 +14337,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>112037</t>
+          <t>112446</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>148901</t>
+          <t>148877</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -14392,12 +14392,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>218161</t>
+          <t>220831</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281653</t>
+          <t>279864</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -14407,12 +14407,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,08%</t>
         </is>
       </c>
     </row>
@@ -14435,12 +14435,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>345665</t>
+          <t>343741</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>397594</t>
+          <t>395882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14450,12 +14450,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>76,7%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14470,12 +14470,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>331361</t>
+          <t>333673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>371468</t>
+          <t>372560</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -14485,12 +14485,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14505,12 +14505,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>689532</t>
+          <t>691990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>754429</t>
+          <t>755037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14520,12 +14520,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,07%</t>
         </is>
       </c>
     </row>
@@ -14665,12 +14665,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22943</t>
+          <t>22118</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>45149</t>
+          <t>43966</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14680,12 +14680,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14700,12 +14700,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38948</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14715,12 +14715,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>47649</t>
+          <t>47281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75994</t>
+          <t>74941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -14778,12 +14778,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27765</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>48432</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14793,82 +14793,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>15,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>49414</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>39085</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>60889</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>11,25%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>17,53%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>86349</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>72926</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>102878</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>11,01%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>15,53%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>49414</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38686</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>60984</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>14,23%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>17,56%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>86349</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>71478</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>103552</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>10,79%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -14891,12 +14891,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229959</t>
+          <t>231393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>259018</t>
+          <t>260068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14906,12 +14906,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14926,12 +14926,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>256293</t>
+          <t>255356</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>282766</t>
+          <t>282466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14941,12 +14941,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14961,12 +14961,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>496595</t>
+          <t>493807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535898</t>
+          <t>533500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14976,12 +14976,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,55%</t>
         </is>
       </c>
     </row>
@@ -15121,12 +15121,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17642</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38869</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -15136,82 +15136,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>5,72%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>36825</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23308</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>53848</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>11,33%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>63342</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>44402</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>82295</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36825</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>22979</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>51928</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>7,75%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>63342</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>44996</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>83724</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -15234,12 +15234,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38322</t>
+          <t>37645</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>68428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15269,12 +15269,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>53974</t>
+          <t>55271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>256211</t>
+          <t>263359</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -15284,12 +15284,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -15304,12 +15304,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>104271</t>
+          <t>104987</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>344515</t>
+          <t>340963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -15319,12 +15319,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>43,29%</t>
         </is>
       </c>
     </row>
@@ -15347,12 +15347,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>216044</t>
+          <t>217231</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>251541</t>
+          <t>250853</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15382,12 +15382,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207840</t>
+          <t>192165</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>380443</t>
+          <t>379857</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -15397,12 +15397,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15417,12 +15417,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>400657</t>
+          <t>400030</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>616598</t>
+          <t>616104</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15432,12 +15432,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,22%</t>
         </is>
       </c>
     </row>
@@ -15577,82 +15577,82 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>832</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>832</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>2619</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,32%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>832</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15690,12 +15690,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9513</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>23252</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15705,12 +15705,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -15725,12 +15725,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17988</t>
+          <t>18986</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15740,12 +15740,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -15760,12 +15760,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>17989</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>38275</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15775,12 +15775,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -15803,12 +15803,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>155490</t>
+          <t>154910</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>169528</t>
+          <t>169229</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15818,47 +15818,47 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>94,68%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>244639</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>237798</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>250834</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
           <t>94,85%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>244639</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>238655</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>251448</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>94,85%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>398351</t>
+          <t>397385</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>418104</t>
+          <t>417100</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15888,12 +15888,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,52%</t>
         </is>
       </c>
     </row>
@@ -16033,12 +16033,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10221</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24937</t>
+          <t>25623</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -16068,12 +16068,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25972</t>
+          <t>24733</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -16083,12 +16083,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16103,12 +16103,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25135</t>
+          <t>23670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>46746</t>
+          <t>44294</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -16118,12 +16118,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -16146,12 +16146,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18608</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -16161,12 +16161,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8495</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>18737</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -16196,12 +16196,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -16216,12 +16216,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>17756</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33109</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -16231,12 +16231,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,42%</t>
         </is>
       </c>
     </row>
@@ -16259,12 +16259,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231426</t>
+          <t>230727</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>249734</t>
+          <t>249491</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -16274,12 +16274,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16294,12 +16294,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>217427</t>
+          <t>217185</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>233701</t>
+          <t>233665</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16309,12 +16309,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16329,12 +16329,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>453843</t>
+          <t>453608</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>477789</t>
+          <t>479284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16344,12 +16344,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -16489,12 +16489,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>103102</t>
+          <t>99660</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>146131</t>
+          <t>144732</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -16504,12 +16504,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16524,12 +16524,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>164308</t>
+          <t>166635</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>592032</t>
+          <t>590578</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -16539,12 +16539,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16559,12 +16559,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>282321</t>
+          <t>282724</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>826945</t>
+          <t>838038</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -16574,12 +16574,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>56,94%</t>
         </is>
       </c>
     </row>
@@ -16602,12 +16602,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>85385</t>
+          <t>83438</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>125751</t>
+          <t>124814</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -16617,12 +16617,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16637,12 +16637,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>55787</t>
+          <t>56928</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>164114</t>
+          <t>164628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16672,12 +16672,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>142513</t>
+          <t>137185</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>268223</t>
+          <t>269209</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16687,12 +16687,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -16715,12 +16715,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>372592</t>
+          <t>372954</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>423478</t>
+          <t>426914</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>67,87%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -16750,12 +16750,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>199603</t>
+          <t>198127</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>528030</t>
+          <t>522921</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16765,12 +16765,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16785,12 +16785,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>501921</t>
+          <t>493502</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>933016</t>
+          <t>933283</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16800,12 +16800,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,41%</t>
         </is>
       </c>
     </row>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>13210</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>51260</t>
+          <t>51946</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -16960,12 +16960,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16980,12 +16980,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>41101</t>
+          <t>40612</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>64788</t>
+          <t>63620</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16995,12 +16995,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -17015,12 +17015,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>52205</t>
+          <t>53014</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>106376</t>
+          <t>108041</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -17030,12 +17030,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -17058,12 +17058,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>27241</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>96214</t>
+          <t>95817</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -17093,12 +17093,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>68051</t>
+          <t>68615</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>98859</t>
+          <t>98543</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -17108,12 +17108,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17128,12 +17128,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>92044</t>
+          <t>89206</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>184624</t>
+          <t>183115</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -17143,12 +17143,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -17171,12 +17171,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>788198</t>
+          <t>786675</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>889340</t>
+          <t>884543</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17206,12 +17206,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>564296</t>
+          <t>565380</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>601379</t>
+          <t>600599</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -17221,12 +17221,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17241,12 +17241,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1360784</t>
+          <t>1362705</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1500135</t>
+          <t>1500535</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -17256,12 +17256,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,18%</t>
         </is>
       </c>
     </row>
@@ -17401,12 +17401,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>212815</t>
+          <t>207074</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>306624</t>
+          <t>310529</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17416,12 +17416,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17436,12 +17436,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>317340</t>
+          <t>313415</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1101682</t>
+          <t>1111643</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17451,12 +17451,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17471,12 +17471,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>570529</t>
+          <t>568924</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1474286</t>
+          <t>1466265</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17486,12 +17486,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -17514,12 +17514,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>319702</t>
+          <t>335004</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>469221</t>
+          <t>473837</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17529,12 +17529,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17549,12 +17549,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>448277</t>
+          <t>446845</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>735213</t>
+          <t>728721</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17564,12 +17564,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17584,12 +17584,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>826305</t>
+          <t>843507</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1164285</t>
+          <t>1158282</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17599,12 +17599,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -17627,12 +17627,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2703469</t>
+          <t>2695481</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>2941023</t>
+          <t>2912984</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17662,12 +17662,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2164050</t>
+          <t>2165341</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>2853912</t>
+          <t>2848636</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17677,12 +17677,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>58,39%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17697,12 +17697,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>4873202</t>
+          <t>4899739</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5654232</t>
+          <t>5653815</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17712,7 +17712,7 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>68,02%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
